--- a/dist/downloads/货价监控指标-26.07.30.xlsx
+++ b/dist/downloads/货价监控指标-26.07.30.xlsx
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="167">
   <si>
     <t xml:space="preserve">截止日期</t>
   </si>
@@ -2859,14 +2859,14 @@
       </c>
       <c r="I6" s="9" t="n">
         <f aca="false">D6/H6</f>
-        <v>0.957368167620706</v>
+        <v>0.957368167620705</v>
       </c>
       <c r="J6" s="8" t="n">
         <v>67210000</v>
       </c>
       <c r="K6" s="9" t="n">
         <f aca="false">D6/J6</f>
-        <v>0.957148583342509</v>
+        <v>0.957148583342508</v>
       </c>
       <c r="L6" s="10"/>
     </row>
@@ -2889,14 +2889,14 @@
       </c>
       <c r="G7" s="9" t="n">
         <f aca="false">D7/F7-1</f>
-        <v>-0.100103903360995</v>
+        <v>-0.100103903360996</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>123516016.722541</v>
       </c>
       <c r="I7" s="9" t="n">
         <f aca="false">D7/H7</f>
-        <v>0.722124694959114</v>
+        <v>0.722124694959116</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>124322207.1</v>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="I9" s="9" t="n">
         <f aca="false">D9/H9</f>
-        <v>0.965751834654499</v>
+        <v>0.965751834654498</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>83471419</v>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="I10" s="9" t="n">
         <f aca="false">D10/H10</f>
-        <v>0.94897761091715</v>
+        <v>0.948977610917151</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>62400000</v>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="I11" s="9" t="n">
         <f aca="false">D11/H11</f>
-        <v>0.753997233610168</v>
+        <v>0.753997233610167</v>
       </c>
       <c r="J11" s="8" t="n">
         <v>58664858.36</v>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="G12" s="9" t="n">
         <f aca="false">D12/F12-1</f>
-        <v>0.0130476828214288</v>
+        <v>0.0130476828214283</v>
       </c>
       <c r="H12" s="8" t="n">
         <f aca="false">SUM(H6:H11)</f>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="I12" s="9" t="n">
         <f aca="false">D12/H12</f>
-        <v>0.860618930406853</v>
+        <v>0.860618930406854</v>
       </c>
       <c r="J12" s="8" t="n">
         <f aca="false">SUM(J6:J11)</f>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">D18/C18</f>
-        <v>0.783854285034398</v>
+        <v>0.783854285034399</v>
       </c>
       <c r="F18" s="8" t="n">
         <f aca="false">K18+F7+P18+U18+Z18+AE18+AJ18</f>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="E23" s="9" t="n">
         <f aca="false">D23/C23</f>
-        <v>0.87368041126555</v>
+        <v>0.873680411265551</v>
       </c>
       <c r="F23" s="8" t="n">
         <f aca="false">K23+F12+P23+U23+Z23+AE23+AJ23</f>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="G23" s="9" t="n">
         <f aca="false">D23/F23-1</f>
-        <v>-0.00252298381997729</v>
+        <v>-0.00252298381997751</v>
       </c>
       <c r="H23" s="8" t="n">
         <f aca="false">SUM(H17:H22)</f>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="E69" s="20" t="n">
         <f aca="false">D69-C69</f>
-        <v>-0.0301256903463881</v>
+        <v>-0.030125690346388</v>
       </c>
       <c r="F69" s="20" t="n">
         <f aca="false">AVERAGE(C69,I69,L69,O69,R69,U69,X69)</f>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="E70" s="20" t="n">
         <f aca="false">D70-C70</f>
-        <v>-0.0982456478401382</v>
+        <v>-0.098245647840139</v>
       </c>
       <c r="F70" s="20" t="n">
         <f aca="false">AVERAGE(C70,I70,L70,O70,R70,U70,X70)</f>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="H70" s="20" t="n">
         <f aca="false">G70-F70</f>
-        <v>-0.0416482504549784</v>
+        <v>-0.0416482504549786</v>
       </c>
       <c r="I70" s="20" t="n">
         <v>0.944438752945</v>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="E71" s="20" t="n">
         <f aca="false">D71-C71</f>
-        <v>-0.11769259702196</v>
+        <v>-0.117692597021959</v>
       </c>
       <c r="F71" s="20" t="n">
         <f aca="false">AVERAGE(C71,I71,L71,O71,R71,U71,X71)</f>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="H71" s="20" t="n">
         <f aca="false">G71-F71</f>
-        <v>-0.0378472130799559</v>
+        <v>-0.0378472130799556</v>
       </c>
       <c r="I71" s="20" t="n">
         <v>0.937773921148</v>
@@ -7560,7 +7560,7 @@
       </c>
       <c r="E72" s="20" t="n">
         <f aca="false">D72-C72</f>
-        <v>-0.0593607786320467</v>
+        <v>-0.059360778632047</v>
       </c>
       <c r="F72" s="20" t="n">
         <f aca="false">AVERAGE(C72,I72,L72,O72,R72,U72,X72)</f>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="H72" s="20" t="n">
         <f aca="false">G72-F72</f>
-        <v>-0.0612745002992114</v>
+        <v>-0.0612745002992116</v>
       </c>
       <c r="I72" s="20" t="n">
         <v>0.940199129414</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="E73" s="20" t="n">
         <f aca="false">D73-C73</f>
-        <v>-0.0493063148488317</v>
+        <v>-0.049306314848832</v>
       </c>
       <c r="F73" s="20" t="n">
         <f aca="false">AVERAGE(C73,I73,L73,O73,R73,U73,X73)</f>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="H73" s="20" t="n">
         <f aca="false">G73-F73</f>
-        <v>-0.0660683045855575</v>
+        <v>-0.0660683045855576</v>
       </c>
       <c r="I73" s="20" t="n">
         <v>0.949920445348</v>
@@ -7992,50 +7992,50 @@
         <v>105</v>
       </c>
       <c r="C81" s="42" t="n">
-        <v>316.12</v>
+        <v>1405.14285714286</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>0.708971276730356</v>
+        <v>0.7095109800732</v>
       </c>
       <c r="E81" s="12" t="n">
-        <v>0.882393</v>
+        <v>0.894438</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0.8066</v>
+        <v>0.8146325152</v>
       </c>
       <c r="G81" s="9" t="n">
         <f aca="false">IFERROR(E81-F81,"(NULL)")</f>
-        <v>0.075793</v>
+        <v>0.0798054847999999</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>0.88357</v>
+        <v>0.884556</v>
       </c>
       <c r="I81" s="12" t="n">
         <v>0.8207995184</v>
       </c>
       <c r="J81" s="9" t="n">
         <f aca="false">IFERROR(H81-I81,"(NULL)")</f>
-        <v>0.0627704816</v>
+        <v>0.0637564816</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>0.952380952380952</v>
+        <v>0.819371727748691</v>
       </c>
       <c r="L81" s="12" t="n">
         <v>0.8082191781</v>
       </c>
       <c r="M81" s="9" t="n">
         <f aca="false">IFERROR(K81-L81,"(NULL)")</f>
-        <v>0.144161774280952</v>
+        <v>0.0111525496486911</v>
       </c>
       <c r="N81" s="12" t="n">
-        <v>0.0477760119292876</v>
+        <v>0.0762847946804372</v>
       </c>
       <c r="O81" s="12" t="n">
         <v>0.0611152139</v>
       </c>
       <c r="P81" s="9" t="n">
         <f aca="false">IFERROR(N81-O81,"(NULL)")</f>
-        <v>-0.0133392019707124</v>
+        <v>0.0151695807804372</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8043,50 +8043,50 @@
         <v>15</v>
       </c>
       <c r="C82" s="42" t="n">
-        <v>876.72</v>
+        <v>116.535714285714</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>0.807053563281321</v>
+        <v>0.251608948820104</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>0.916081</v>
+        <v>0.734317</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>0.8078</v>
+        <v>0.7556221149</v>
       </c>
       <c r="G82" s="9" t="n">
         <f aca="false">IFERROR(E82-F82,"(NULL)")</f>
-        <v>0.108281</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>0.896254</v>
+        <v>-0.0213051149</v>
+      </c>
+      <c r="H82" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="I82" s="12" t="n">
         <v>0.8207995184</v>
       </c>
-      <c r="J82" s="9" t="n">
+      <c r="J82" s="9" t="str">
         <f aca="false">IFERROR(H82-I82,"(NULL)")</f>
-        <v>0.0754544816</v>
+        <v>(NULL)</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>0.805460750853242</v>
+        <v>0.8</v>
       </c>
       <c r="L82" s="12" t="n">
         <v>0.8082191781</v>
       </c>
       <c r="M82" s="9" t="n">
         <f aca="false">IFERROR(K82-L82,"(NULL)")</f>
-        <v>-0.00275842724675768</v>
+        <v>-0.00821917809999995</v>
       </c>
       <c r="N82" s="12" t="n">
-        <v>0.0891388851887284</v>
+        <v>0.148962148962149</v>
       </c>
       <c r="O82" s="12" t="n">
         <v>0.0611152139</v>
       </c>
       <c r="P82" s="9" t="n">
         <f aca="false">IFERROR(N82-O82,"(NULL)")</f>
-        <v>0.0280236712887284</v>
+        <v>0.087846935062149</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8094,50 +8094,50 @@
         <v>13</v>
       </c>
       <c r="C83" s="42" t="n">
-        <v>1</v>
+        <v>313.964285714286</v>
       </c>
       <c r="D83" s="12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E83" s="12" t="s">
-        <v>86</v>
+        <v>0.710271868956888</v>
+      </c>
+      <c r="E83" s="12" t="n">
+        <v>0.882758</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>0.8417108422</v>
-      </c>
-      <c r="G83" s="9" t="str">
+        <v>0.8066</v>
+      </c>
+      <c r="G83" s="9" t="n">
         <f aca="false">IFERROR(E83-F83,"(NULL)")</f>
-        <v>(NULL)</v>
+        <v>0.0761580000000001</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>0.999768</v>
+        <v>0.882866</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>0.8207995184</v>
       </c>
       <c r="J83" s="9" t="n">
         <f aca="false">IFERROR(H83-I83,"(NULL)")</f>
-        <v>0.1789684816</v>
-      </c>
-      <c r="K83" s="12" t="s">
-        <v>86</v>
+        <v>0.0620664816000001</v>
+      </c>
+      <c r="K83" s="12" t="n">
+        <v>0.893333333333333</v>
       </c>
       <c r="L83" s="12" t="n">
         <v>0.8082191781</v>
       </c>
-      <c r="M83" s="9" t="str">
+      <c r="M83" s="9" t="n">
         <f aca="false">IFERROR(K83-L83,"(NULL)")</f>
-        <v>(NULL)</v>
+        <v>0.0851141552333333</v>
       </c>
       <c r="N83" s="12" t="n">
-        <v>0</v>
+        <v>0.0462958062068844</v>
       </c>
       <c r="O83" s="12" t="n">
         <v>0.0611152139</v>
       </c>
       <c r="P83" s="9" t="n">
         <f aca="false">IFERROR(N83-O83,"(NULL)")</f>
-        <v>-0.0611152139</v>
+        <v>-0.0148194076931156</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8145,50 +8145,50 @@
         <v>14</v>
       </c>
       <c r="C84" s="42" t="n">
-        <v>1.68</v>
+        <v>875.75</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>0.785714285714286</v>
-      </c>
-      <c r="E84" s="12" t="s">
-        <v>86</v>
+        <v>0.806247706047877</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>0.916198</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0.7771375317</v>
-      </c>
-      <c r="G84" s="9" t="str">
+        <v>0.8078</v>
+      </c>
+      <c r="G84" s="9" t="n">
         <f aca="false">IFERROR(E84-F84,"(NULL)")</f>
-        <v>(NULL)</v>
-      </c>
-      <c r="H84" s="12" t="s">
-        <v>86</v>
+        <v>0.108398</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>0.89528</v>
       </c>
       <c r="I84" s="12" t="n">
         <v>0.8207995184</v>
       </c>
-      <c r="J84" s="9" t="str">
+      <c r="J84" s="9" t="n">
         <f aca="false">IFERROR(H84-I84,"(NULL)")</f>
-        <v>(NULL)</v>
-      </c>
-      <c r="K84" s="12" t="s">
-        <v>86</v>
+        <v>0.0744804816</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>0.804054054054054</v>
       </c>
       <c r="L84" s="12" t="n">
         <v>0.8082191781</v>
       </c>
-      <c r="M84" s="9" t="str">
+      <c r="M84" s="9" t="n">
         <f aca="false">IFERROR(K84-L84,"(NULL)")</f>
-        <v>(NULL)</v>
+        <v>-0.00416512404594593</v>
       </c>
       <c r="N84" s="12" t="n">
-        <v>0.208955223880597</v>
+        <v>0.0917371996811781</v>
       </c>
       <c r="O84" s="12" t="n">
         <v>0.0611152139</v>
       </c>
       <c r="P84" s="9" t="n">
         <f aca="false">IFERROR(N84-O84,"(NULL)")</f>
-        <v>0.147840009980597</v>
+        <v>0.0306219857811781</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8196,50 +8196,50 @@
         <v>16</v>
       </c>
       <c r="C85" s="42" t="n">
-        <v>96.8</v>
+        <v>1</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>0.381404958677686</v>
-      </c>
-      <c r="E85" s="12" t="n">
-        <v>0.847162</v>
+        <v>0.8</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>0.8087257009</v>
-      </c>
-      <c r="G85" s="9" t="n">
+        <v>0.8417108422</v>
+      </c>
+      <c r="G85" s="9" t="str">
         <f aca="false">IFERROR(E85-F85,"(NULL)")</f>
-        <v>0.0384362991</v>
+        <v>(NULL)</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>0.789895</v>
+        <v>0.999768</v>
       </c>
       <c r="I85" s="12" t="n">
         <v>0.8207995184</v>
       </c>
       <c r="J85" s="9" t="n">
         <f aca="false">IFERROR(H85-I85,"(NULL)")</f>
-        <v>-0.0309045184</v>
-      </c>
-      <c r="K85" s="12" t="n">
-        <v>0.666666666666667</v>
+        <v>0.1789684816</v>
+      </c>
+      <c r="K85" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="L85" s="12" t="n">
         <v>0.8082191781</v>
       </c>
-      <c r="M85" s="9" t="n">
+      <c r="M85" s="9" t="str">
         <f aca="false">IFERROR(K85-L85,"(NULL)")</f>
-        <v>-0.141552511433333</v>
+        <v>(NULL)</v>
       </c>
       <c r="N85" s="12" t="n">
-        <v>0.0181731229076997</v>
+        <v>0</v>
       </c>
       <c r="O85" s="12" t="n">
         <v>0.0611152139</v>
       </c>
       <c r="P85" s="9" t="n">
         <f aca="false">IFERROR(N85-O85,"(NULL)")</f>
-        <v>-0.0429420909923003</v>
+        <v>-0.0611152139</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="H116" s="8" t="n">
         <f aca="false">SUM(H117:H119)</f>
-        <v>4987710.7085655</v>
+        <v>4987710.70856549</v>
       </c>
       <c r="I116" s="9" t="n">
         <f aca="false">D116/H116</f>
@@ -9730,7 +9730,7 @@
       </c>
       <c r="I118" s="9" t="n">
         <f aca="false">D118/H118</f>
-        <v>0.0724962454977658</v>
+        <v>0.0724962454977659</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="H119" s="8" t="n">
         <f aca="false">C119*H12/C12</f>
-        <v>897787.927541791</v>
+        <v>897787.92754179</v>
       </c>
       <c r="I119" s="9" t="n">
         <f aca="false">D119/H119</f>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="E132" s="9" t="n">
         <f aca="false">D132/C132</f>
-        <v>1.6441751174652</v>
+        <v>1.64417511746521</v>
       </c>
       <c r="F132" s="8" t="n">
         <v>2.0376362786555</v>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="H133" s="8" t="n">
         <f aca="false">C133*H12/C12</f>
-        <v>0.00698808560491612</v>
+        <v>0.00698808560491611</v>
       </c>
       <c r="I133" s="12" t="n">
         <v>11419110</v>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="I135" s="12" t="n">
         <f aca="false">D135/H135</f>
-        <v>0.388152800111978</v>
+        <v>0.388152800111979</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="E140" s="9" t="n">
         <f aca="false">D140/C140</f>
-        <v>0.388467389082298</v>
+        <v>0.388467389082299</v>
       </c>
       <c r="F140" s="8" t="n">
         <f aca="false">SUM(F141:F143)</f>
@@ -10722,7 +10722,7 @@
       </c>
       <c r="C141" s="8" t="n">
         <f aca="false">H141+H133+M141+R141+W141+AB141+AG141</f>
-        <v>0.00698808560491612</v>
+        <v>0.00698808560491611</v>
       </c>
       <c r="D141" s="8" t="n">
         <f aca="false">I141+D133+N141+S141+X141+AC141+AH141</f>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="E143" s="9" t="n">
         <f aca="false">D143/C143</f>
-        <v>0.388152800111978</v>
+        <v>0.388152800111979</v>
       </c>
       <c r="F143" s="8" t="n">
         <f aca="false">K143+F135+P143+U143+Z143+AE143+AJ143</f>

--- a/dist/downloads/货价监控指标-26.07.30.xlsx
+++ b/dist/downloads/货价监控指标-26.07.30.xlsx
@@ -4753,25 +4753,25 @@
         <v>0.795681</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>0.841959</v>
+        <v>0.8408039576</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>-4.6278</v>
+        <v>-4.5123</v>
       </c>
       <c r="K46" s="28" t="n">
-        <v>-2</v>
+        <v>0.820804</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>0.982295</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>0.872659</v>
+        <v>0.8408039576</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>10.9636</v>
+        <v>14.1491</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>-2</v>
+        <v>0.851804</v>
       </c>
       <c r="P46" s="4"/>
     </row>
@@ -4798,25 +4798,25 @@
         <v>0.867312</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>0.838881</v>
+        <v>0.8393465983</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>2.8431</v>
+        <v>2.7965</v>
       </c>
       <c r="K47" s="28" t="n">
-        <v>-2</v>
+        <v>0.819347</v>
       </c>
       <c r="L47" s="12" t="n">
         <v>0.950493</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>0.869581</v>
+        <v>0.8393465983</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>8.09120000000002</v>
+        <v>11.1146</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>-2</v>
+        <v>0.850347</v>
       </c>
       <c r="P47" s="4"/>
     </row>
@@ -4843,25 +4843,25 @@
         <v>0.744074</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>0.775292</v>
+        <v>0.777447231</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>-3.1218</v>
+        <v>-3.3373</v>
       </c>
       <c r="K48" s="28" t="n">
-        <v>-2</v>
+        <v>0.757447</v>
       </c>
       <c r="L48" s="12" t="n">
         <v>0.725828</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>0.805992</v>
+        <v>0.777447231</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>-8.01639999999999</v>
+        <v>-5.1619</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>-2</v>
+        <v>0.788447</v>
       </c>
       <c r="P48" s="4"/>
     </row>
@@ -4888,25 +4888,25 @@
         <v>0.810591</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>0.829261</v>
+        <v>0.8296242895</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>-1.867</v>
+        <v>-1.9033</v>
       </c>
       <c r="K49" s="28" t="n">
-        <v>-2</v>
+        <v>0.809624</v>
       </c>
       <c r="L49" s="12" t="n">
         <v>0.870032</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>0.859961</v>
+        <v>0.8296242895</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>1.00710000000001</v>
+        <v>4.0408</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>-2</v>
+        <v>0.840624</v>
       </c>
       <c r="P49" s="4"/>
     </row>
@@ -4933,25 +4933,25 @@
         <v>0.887928</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>0.834024</v>
+        <v>0.8344423592</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>5.3904</v>
+        <v>5.3486</v>
       </c>
       <c r="K50" s="28" t="n">
-        <v>-2</v>
+        <v>0.814442</v>
       </c>
       <c r="L50" s="12" t="n">
         <v>0.885792</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>0.864724</v>
+        <v>0.8344423592</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>2.10680000000001</v>
+        <v>5.135</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>-2</v>
+        <v>0.845442</v>
       </c>
       <c r="P50" s="4"/>
     </row>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>0.726978</v>
+        <v>0.733507</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>0.847102</v>
+        <v>0.8567400971</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>-12.0124</v>
+        <v>-12.3233</v>
       </c>
       <c r="K51" s="28" t="n">
-        <v>-2</v>
+        <v>0.83674</v>
       </c>
       <c r="L51" s="12" t="s">
         <v>86</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>0.877802</v>
+        <v>0.8567400971</v>
       </c>
       <c r="N51" s="12" t="s">
         <v>86</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>-2</v>
+        <v>0.86774</v>
       </c>
       <c r="P51" s="4"/>
     </row>
@@ -5005,43 +5005,43 @@
         <v>19</v>
       </c>
       <c r="C52" s="29" t="n">
-        <v>0</v>
+        <v>60.00589491</v>
       </c>
       <c r="D52" s="30" t="n">
-        <v>0</v>
+        <v>68.73</v>
       </c>
       <c r="E52" s="30" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>0.870676</v>
+        <v>0.873067</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.129324</v>
+        <v>0.126933</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>0.821891</v>
+        <v>0.819409</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>0.820605</v>
+        <v>0.8243722094</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>0.1286</v>
+        <v>-0.4963</v>
       </c>
       <c r="K52" s="28" t="n">
-        <v>-2</v>
+        <v>0.804372</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>0.871534</v>
+        <v>0.866168</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>0.851305</v>
+        <v>0.8243722094</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>2.02290000000001</v>
+        <v>4.1796</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>-2</v>
+        <v>0.835372</v>
       </c>
       <c r="P52" s="4"/>
     </row>
@@ -5410,11 +5410,11 @@
       </c>
       <c r="I57" s="12" t="n">
         <f aca="false">AVERAGE(I46-2%,P57-2%,AA57-2%,AL57-2%,AW57-2%,BH57-2%,BS57-2%)</f>
-        <v>0.781290851203346</v>
+        <v>0.781125845146204</v>
       </c>
       <c r="J57" s="12" t="n">
         <f aca="false">(H57-I57)*100</f>
-        <v>0.597944085375401</v>
+        <v>0.614444691089677</v>
       </c>
       <c r="K57" s="12" t="n">
         <f aca="false">IFERROR(AVERAGE(L46,R57,AC57,AN57,AY57,BJ57,BU57),"(NULL)")</f>
@@ -5422,11 +5422,11 @@
       </c>
       <c r="L57" s="12" t="n">
         <f aca="false">AVERAGE(M46-2%,S57-2%,AD57-2%,AO57-2%,AZ57-2%,BK57-2%,BV57-2%)</f>
-        <v>0.811990851203347</v>
+        <v>0.807440130860489</v>
       </c>
       <c r="M57" s="12" t="n">
         <f aca="false">IFERROR(((K57-L57)*100),"(NULL)")</f>
-        <v>15.2212933943126</v>
+        <v>15.6763654285983</v>
       </c>
       <c r="N57" s="26" t="n">
         <v>71.8851437589701</v>
@@ -5641,11 +5641,11 @@
       </c>
       <c r="D58" s="27" t="n">
         <f aca="false">IF((J58/(-2)*40+60)&gt;120,120,IF(J58&gt;0,0,(J58/(-2)*40+60)))</f>
-        <v>91.2670452365633</v>
+        <v>91.4000733222777</v>
       </c>
       <c r="E58" s="27" t="n">
         <f aca="false">IFERROR(IF((M58/(-2)*40+60)&gt;120,120,IF(M58&gt;0,0,(M58/(-2)*40+60))),"(NULL)")</f>
-        <v>93.9554840293364</v>
+        <v>85.3170835436223</v>
       </c>
       <c r="F58" s="12" t="n">
         <f aca="false">SUM(U58,AF58,AQ58,BB58,BM58,BX58)/SUM(U58:V58,AF58:AG58,AQ58:AR58,BB58:BC58,BM58:BN58,BX58:BY58)</f>
@@ -5661,11 +5661,11 @@
       </c>
       <c r="I58" s="12" t="n">
         <f aca="false">AVERAGE(I47-2%,P58-2%,AA58-2%,AL58-2%,AW58-2%,BH58-2%,BS58-2%)</f>
-        <v>0.787804327736616</v>
+        <v>0.787870841779473</v>
       </c>
       <c r="J58" s="12" t="n">
         <f aca="false">(H58-I58)*100</f>
-        <v>-1.56335226182817</v>
+        <v>-1.57000366611388</v>
       </c>
       <c r="K58" s="12" t="n">
         <f aca="false">IFERROR(AVERAGE(L47,R58,AC58,AN58,AY58,BJ58,BU58),"(NULL)")</f>
@@ -5673,11 +5673,11 @@
       </c>
       <c r="L58" s="12" t="n">
         <f aca="false">AVERAGE(M47-2%,S58-2%,AD58-2%,AO58-2%,AZ58-2%,BK58-2%,BV58-2%)</f>
-        <v>0.818504327736616</v>
+        <v>0.814185127493759</v>
       </c>
       <c r="M58" s="12" t="n">
         <f aca="false">IFERROR(((K58-L58)*100),"(NULL)")</f>
-        <v>-1.69777420146682</v>
+        <v>-1.26585417718111</v>
       </c>
       <c r="N58" s="26" t="n">
         <v>119.335376267249</v>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="D59" s="27" t="n">
         <f aca="false">IF((J59/(-2)*40+60)&gt;120,120,IF(J59&gt;0,0,(J59/(-2)*40+60)))</f>
-        <v>105.690825899232</v>
+        <v>106.306606184946</v>
       </c>
       <c r="E59" s="27" t="n">
         <f aca="false">IFERROR(IF((M59/(-2)*40+60)&gt;120,120,IF(M59&gt;0,0,(M59/(-2)*40+60))),"(NULL)")</f>
@@ -5912,11 +5912,11 @@
       </c>
       <c r="I59" s="12" t="n">
         <f aca="false">AVERAGE(I48-2%,P59-2%,AA59-2%,AL59-2%,AW59-2%,BH59-2%,BS59-2%)</f>
-        <v>0.778238583933542</v>
+        <v>0.778546474076399</v>
       </c>
       <c r="J59" s="12" t="n">
         <f aca="false">(H59-I59)*100</f>
-        <v>-2.28454129496161</v>
+        <v>-2.31533030924731</v>
       </c>
       <c r="K59" s="12" t="n">
         <f aca="false">IFERROR(AVERAGE(L48,R59,AC59,AN59,AY59,BJ59,BU59),"(NULL)")</f>
@@ -5924,11 +5924,11 @@
       </c>
       <c r="L59" s="12" t="n">
         <f aca="false">AVERAGE(M48-2%,S59-2%,AD59-2%,AO59-2%,AZ59-2%,BK59-2%,BV59-2%)</f>
-        <v>0.808938583933542</v>
+        <v>0.804860759790685</v>
       </c>
       <c r="M59" s="12" t="n">
         <f aca="false">IFERROR(((K59-L59)*100),"(NULL)")</f>
-        <v>-5.06511950234946</v>
+        <v>-4.65733708806374</v>
       </c>
       <c r="N59" s="26" t="n">
         <v>120</v>
@@ -6163,11 +6163,11 @@
       </c>
       <c r="I60" s="12" t="n">
         <f aca="false">AVERAGE(I49-2%,P60-2%,AA60-2%,AL60-2%,AW60-2%,BH60-2%,BS60-2%)</f>
-        <v>0.817761128688366</v>
+        <v>0.817813027188365</v>
       </c>
       <c r="J60" s="12" t="n">
         <f aca="false">(H60-I60)*100</f>
-        <v>1.02228094132308</v>
+        <v>1.01709109132309</v>
       </c>
       <c r="K60" s="12" t="n">
         <f aca="false">IFERROR(AVERAGE(L49,R60,AC60,AN60,AY60,BJ60,BU60),"(NULL)")</f>
@@ -6175,11 +6175,11 @@
       </c>
       <c r="L60" s="12" t="n">
         <f aca="false">AVERAGE(M49-2%,S60-2%,AD60-2%,AO60-2%,AZ60-2%,BK60-2%,BV60-2%)</f>
-        <v>0.848461128688365</v>
+        <v>0.844127312902651</v>
       </c>
       <c r="M60" s="12" t="n">
         <f aca="false">IFERROR(((K60-L60)*100),"(NULL)")</f>
-        <v>4.3163247534796</v>
+        <v>4.74970633205101</v>
       </c>
       <c r="N60" s="26" t="n">
         <v>0</v>
@@ -6414,11 +6414,11 @@
       </c>
       <c r="I61" s="12" t="n">
         <f aca="false">AVERAGE(I50-2%,P61-2%,AA61-2%,AL61-2%,AW61-2%,BH61-2%,BS61-2%)</f>
-        <v>0.793219752133375</v>
+        <v>0.793279517733375</v>
       </c>
       <c r="J61" s="12" t="n">
         <f aca="false">(H61-I61)*100</f>
-        <v>7.37460813876164</v>
+        <v>7.36863157876164</v>
       </c>
       <c r="K61" s="12" t="n">
         <f aca="false">IFERROR(AVERAGE(L50,R61,AC61,AN61,AY61,BJ61,BU61),"(NULL)")</f>
@@ -6426,11 +6426,11 @@
       </c>
       <c r="L61" s="12" t="n">
         <f aca="false">AVERAGE(M50-2%,S61-2%,AD61-2%,AO61-2%,AZ61-2%,BK61-2%,BV61-2%)</f>
-        <v>0.823919752133376</v>
+        <v>0.819593803447661</v>
       </c>
       <c r="M61" s="12" t="n">
         <f aca="false">IFERROR(((K61-L61)*100),"(NULL)")</f>
-        <v>0.424974614208862</v>
+        <v>0.857569482780285</v>
       </c>
       <c r="N61" s="26" t="n">
         <v>11.4174663533469</v>
@@ -6661,15 +6661,15 @@
       </c>
       <c r="H62" s="12" t="n">
         <f aca="false">AVERAGE(H51,O62,Z62,AK62,AV62,BG62,BR62)</f>
-        <v>0.772981098442094</v>
+        <v>0.773913812727808</v>
       </c>
       <c r="I62" s="12" t="n">
         <f aca="false">AVERAGE(I51-2%,P62-2%,AA62-2%,AL62-2%,AW62-2%,BH62-2%,BS62-2%)</f>
-        <v>0.80964237094791</v>
+        <v>0.811019241962196</v>
       </c>
       <c r="J62" s="12" t="n">
         <f aca="false">(H62-I62)*100</f>
-        <v>-3.6661272505817</v>
+        <v>-3.71054292343883</v>
       </c>
       <c r="K62" s="12" t="str">
         <f aca="false">IFERROR(AVERAGE(L51,R62,AC62,AN62,AY62,BJ62,BU62),"(NULL)")</f>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="L62" s="12" t="n">
         <f aca="false">AVERAGE(M51-2%,S62-2%,AD62-2%,AO62-2%,AZ62-2%,BK62-2%,BV62-2%)</f>
-        <v>0.840342370947911</v>
+        <v>0.837333527676482</v>
       </c>
       <c r="M62" s="12" t="str">
         <f aca="false">IFERROR(((K62-L62)*100),"(NULL)")</f>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="C63" s="36" t="n">
         <f aca="false">AVERAGE(C52,N63,Y63,AJ63,AU63,BF63,BQ63)</f>
-        <v>32.6462042157164</v>
+        <v>41.218474917145</v>
       </c>
       <c r="D63" s="27" t="n">
         <f aca="false">IF((J63/(-2)*40+60)&gt;120,120,IF(J63&gt;0,0,(J63/(-2)*40+60)))</f>
@@ -6912,27 +6912,27 @@
       </c>
       <c r="H63" s="12" t="n">
         <f aca="false">AVERAGE(H52,O63,Z63,AK63,AV63,BG63,BR63)</f>
-        <v>0.827021439897681</v>
+        <v>0.82666686846911</v>
       </c>
       <c r="I63" s="12" t="n">
         <f aca="false">AVERAGE(I52-2%,P63-2%,AA63-2%,AL63-2%,AW63-2%,BH63-2%,BS63-2%)</f>
-        <v>0.807222611788162</v>
+        <v>0.807760784559591</v>
       </c>
       <c r="J63" s="12" t="n">
         <f aca="false">(H63-I63)*100</f>
-        <v>1.97988281095192</v>
+        <v>1.89060839095191</v>
       </c>
       <c r="K63" s="12" t="n">
         <f aca="false">IFERROR(AVERAGE(L52,R63,AC63,AN63,AY63,BJ63,BU63),"(NULL)")</f>
-        <v>0.865781313364802</v>
+        <v>0.86501474193623</v>
       </c>
       <c r="L63" s="12" t="n">
         <f aca="false">AVERAGE(M52-2%,S63-2%,AD63-2%,AO63-2%,AZ63-2%,BK63-2%,BV63-2%)</f>
-        <v>0.837922611788162</v>
+        <v>0.834075070273876</v>
       </c>
       <c r="M63" s="12" t="n">
         <f aca="false">IFERROR(((K63-L63)*100),"(NULL)")</f>
-        <v>2.78587015766398</v>
+        <v>3.09396716623541</v>
       </c>
       <c r="N63" s="26" t="n">
         <v>0</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="M83" s="9" t="n">
         <f aca="false">IFERROR(K83-L83,"(NULL)")</f>
-        <v>0.0851141552333333</v>
+        <v>0.085114155233333</v>
       </c>
       <c r="N83" s="12" t="n">
         <v>0.0462958062068844</v>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="M84" s="9" t="n">
         <f aca="false">IFERROR(K84-L84,"(NULL)")</f>
-        <v>-0.00416512404594593</v>
+        <v>-0.00416512404594605</v>
       </c>
       <c r="N84" s="12" t="n">
         <v>0.0917371996811781</v>
